--- a/data/Demo_Settings.xlsx
+++ b/data/Demo_Settings.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="461">
   <si>
     <t>Parameter</t>
   </si>
@@ -877,9 +877,6 @@
   </si>
   <si>
     <t>plotFont</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>Size: Axis Text (X)</t>
@@ -3891,71 +3888,71 @@
       <c r="B116" t="s">
         <v>282</v>
       </c>
-      <c r="C116" t="s">
-        <v>283</v>
+      <c r="C116">
+        <v>25</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
+        <v>283</v>
+      </c>
+      <c r="B117" t="s">
         <v>284</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" t="s">
         <v>285</v>
-      </c>
-      <c r="C117" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
+        <v>286</v>
+      </c>
+      <c r="B118" t="s">
         <v>287</v>
       </c>
-      <c r="B118" t="s">
+      <c r="C118" t="s">
         <v>288</v>
-      </c>
-      <c r="C118" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
+        <v>289</v>
+      </c>
+      <c r="B119" t="s">
         <v>290</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C119" t="s">
         <v>291</v>
-      </c>
-      <c r="C119" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
+        <v>292</v>
+      </c>
+      <c r="B120" t="s">
         <v>293</v>
       </c>
-      <c r="B120" t="s">
-        <v>294</v>
-      </c>
       <c r="C120" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
+        <v>294</v>
+      </c>
+      <c r="B121" t="s">
         <v>295</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121" t="s">
         <v>296</v>
-      </c>
-      <c r="C121" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
+        <v>297</v>
+      </c>
+      <c r="B122" t="s">
         <v>298</v>
-      </c>
-      <c r="B122" t="s">
-        <v>299</v>
       </c>
       <c r="C122" t="s">
         <v>28</v>
@@ -3963,98 +3960,98 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
+        <v>299</v>
+      </c>
+      <c r="B123" t="s">
         <v>300</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
         <v>301</v>
-      </c>
-      <c r="C123" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
+        <v>302</v>
+      </c>
+      <c r="B124" t="s">
         <v>303</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C124" t="s">
         <v>304</v>
-      </c>
-      <c r="C124" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
+        <v>305</v>
+      </c>
+      <c r="B125" t="s">
         <v>306</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
         <v>307</v>
-      </c>
-      <c r="C125" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
+        <v>308</v>
+      </c>
+      <c r="B126" t="s">
         <v>309</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" t="s">
         <v>310</v>
-      </c>
-      <c r="C126" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
+        <v>311</v>
+      </c>
+      <c r="B127" t="s">
         <v>312</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" t="s">
         <v>313</v>
-      </c>
-      <c r="C127" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
+        <v>314</v>
+      </c>
+      <c r="B128" t="s">
         <v>315</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
         <v>316</v>
-      </c>
-      <c r="C128" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
+        <v>317</v>
+      </c>
+      <c r="B129" t="s">
         <v>318</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>319</v>
-      </c>
-      <c r="C129" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
+        <v>320</v>
+      </c>
+      <c r="B130" t="s">
         <v>321</v>
       </c>
-      <c r="B130" t="s">
-        <v>322</v>
-      </c>
       <c r="C130" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
+        <v>322</v>
+      </c>
+      <c r="B131" t="s">
         <v>323</v>
-      </c>
-      <c r="B131" t="s">
-        <v>324</v>
       </c>
       <c r="C131" t="s">
         <v>28</v>
@@ -4062,21 +4059,21 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
+        <v>324</v>
+      </c>
+      <c r="B132" t="s">
         <v>325</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
         <v>326</v>
-      </c>
-      <c r="C132" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
+        <v>327</v>
+      </c>
+      <c r="B133" t="s">
         <v>328</v>
-      </c>
-      <c r="B133" t="s">
-        <v>329</v>
       </c>
       <c r="C133" t="s">
         <v>98</v>
@@ -4084,10 +4081,10 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
+        <v>329</v>
+      </c>
+      <c r="B134" t="s">
         <v>330</v>
-      </c>
-      <c r="B134" t="s">
-        <v>331</v>
       </c>
       <c r="C134" t="s">
         <v>98</v>
@@ -4095,21 +4092,21 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
+        <v>331</v>
+      </c>
+      <c r="B135" t="s">
         <v>332</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" t="s">
         <v>333</v>
-      </c>
-      <c r="C135" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
+        <v>334</v>
+      </c>
+      <c r="B136" t="s">
         <v>335</v>
-      </c>
-      <c r="B136" t="s">
-        <v>336</v>
       </c>
       <c r="C136" t="s">
         <v>10</v>
@@ -4117,120 +4114,120 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
+        <v>336</v>
+      </c>
+      <c r="B137" t="s">
         <v>337</v>
       </c>
-      <c r="B137" t="s">
-        <v>338</v>
-      </c>
       <c r="C137" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
+        <v>338</v>
+      </c>
+      <c r="B138" t="s">
         <v>339</v>
       </c>
-      <c r="B138" t="s">
-        <v>340</v>
-      </c>
       <c r="C138" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
+        <v>340</v>
+      </c>
+      <c r="B139" t="s">
         <v>341</v>
       </c>
-      <c r="B139" t="s">
-        <v>342</v>
-      </c>
       <c r="C139" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
+        <v>342</v>
+      </c>
+      <c r="B140" t="s">
         <v>343</v>
       </c>
-      <c r="B140" t="s">
-        <v>344</v>
-      </c>
       <c r="C140" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
+        <v>344</v>
+      </c>
+      <c r="B141" t="s">
         <v>345</v>
       </c>
-      <c r="B141" t="s">
-        <v>346</v>
-      </c>
       <c r="C141" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
+        <v>346</v>
+      </c>
+      <c r="B142" t="s">
         <v>347</v>
       </c>
-      <c r="B142" t="s">
-        <v>348</v>
-      </c>
       <c r="C142" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
+        <v>348</v>
+      </c>
+      <c r="B143" t="s">
         <v>349</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
         <v>350</v>
-      </c>
-      <c r="C143" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
+        <v>351</v>
+      </c>
+      <c r="B144" t="s">
         <v>352</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
         <v>353</v>
-      </c>
-      <c r="C144" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
+        <v>354</v>
+      </c>
+      <c r="B145" t="s">
         <v>355</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C145" t="s">
         <v>356</v>
-      </c>
-      <c r="C145" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
+        <v>357</v>
+      </c>
+      <c r="B146" t="s">
         <v>358</v>
       </c>
-      <c r="B146" t="s">
+      <c r="C146" t="s">
         <v>359</v>
-      </c>
-      <c r="C146" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
+        <v>360</v>
+      </c>
+      <c r="B147" t="s">
         <v>361</v>
-      </c>
-      <c r="B147" t="s">
-        <v>362</v>
       </c>
       <c r="C147" t="s">
         <v>28</v>
@@ -4238,10 +4235,10 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
+        <v>362</v>
+      </c>
+      <c r="B148" t="s">
         <v>363</v>
-      </c>
-      <c r="B148" t="s">
-        <v>364</v>
       </c>
       <c r="C148" t="s">
         <v>224</v>
@@ -4249,21 +4246,21 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
+        <v>364</v>
+      </c>
+      <c r="B149" t="s">
         <v>365</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C149" t="s">
         <v>366</v>
-      </c>
-      <c r="C149" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
+        <v>367</v>
+      </c>
+      <c r="B150" t="s">
         <v>368</v>
-      </c>
-      <c r="B150" t="s">
-        <v>369</v>
       </c>
       <c r="C150" t="s">
         <v>145</v>
@@ -4271,10 +4268,10 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
+        <v>369</v>
+      </c>
+      <c r="B151" t="s">
         <v>370</v>
-      </c>
-      <c r="B151" t="s">
-        <v>371</v>
       </c>
       <c r="C151" t="s">
         <v>101</v>
@@ -4282,32 +4279,32 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
+        <v>371</v>
+      </c>
+      <c r="B152" t="s">
         <v>372</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" t="s">
         <v>373</v>
-      </c>
-      <c r="C152" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
+        <v>374</v>
+      </c>
+      <c r="B153" t="s">
         <v>375</v>
       </c>
-      <c r="B153" t="s">
-        <v>376</v>
-      </c>
       <c r="C153" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
+        <v>376</v>
+      </c>
+      <c r="B154" t="s">
         <v>377</v>
-      </c>
-      <c r="B154" t="s">
-        <v>378</v>
       </c>
       <c r="C154" t="s">
         <v>101</v>
@@ -4315,10 +4312,10 @@
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
+        <v>378</v>
+      </c>
+      <c r="B155" t="s">
         <v>379</v>
-      </c>
-      <c r="B155" t="s">
-        <v>380</v>
       </c>
       <c r="C155" t="s">
         <v>54</v>
@@ -4326,10 +4323,10 @@
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
+        <v>380</v>
+      </c>
+      <c r="B156" t="s">
         <v>381</v>
-      </c>
-      <c r="B156" t="s">
-        <v>382</v>
       </c>
       <c r="C156" t="s">
         <v>25</v>
@@ -4337,10 +4334,10 @@
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
+        <v>382</v>
+      </c>
+      <c r="B157" t="s">
         <v>383</v>
-      </c>
-      <c r="B157" t="s">
-        <v>384</v>
       </c>
       <c r="C157" t="s">
         <v>145</v>
@@ -4348,32 +4345,32 @@
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
+        <v>384</v>
+      </c>
+      <c r="B158" t="s">
         <v>385</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C158" t="s">
         <v>386</v>
-      </c>
-      <c r="C158" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
+        <v>387</v>
+      </c>
+      <c r="B159" t="s">
         <v>388</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C159" t="s">
         <v>389</v>
-      </c>
-      <c r="C159" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
+        <v>390</v>
+      </c>
+      <c r="B160" t="s">
         <v>391</v>
-      </c>
-      <c r="B160" t="s">
-        <v>392</v>
       </c>
       <c r="C160" t="s">
         <v>5</v>
@@ -4381,32 +4378,32 @@
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
+        <v>392</v>
+      </c>
+      <c r="B161" t="s">
         <v>393</v>
       </c>
-      <c r="B161" t="s">
+      <c r="C161" t="s">
         <v>394</v>
-      </c>
-      <c r="C161" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
+        <v>395</v>
+      </c>
+      <c r="B162" t="s">
         <v>396</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C162" t="s">
         <v>397</v>
-      </c>
-      <c r="C162" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
+        <v>398</v>
+      </c>
+      <c r="B163" t="s">
         <v>399</v>
-      </c>
-      <c r="B163" t="s">
-        <v>400</v>
       </c>
       <c r="C163" t="s">
         <v>40</v>
@@ -4414,10 +4411,10 @@
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B164" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C164" t="s">
         <v>40</v>
@@ -4425,10 +4422,10 @@
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B165" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C165" t="s">
         <v>40</v>
@@ -4436,10 +4433,10 @@
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B166" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C166" t="s">
         <v>40</v>
@@ -4447,10 +4444,10 @@
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
+        <v>403</v>
+      </c>
+      <c r="B167" t="s">
         <v>404</v>
-      </c>
-      <c r="B167" t="s">
-        <v>405</v>
       </c>
       <c r="C167" t="s">
         <v>40</v>
@@ -4458,10 +4455,10 @@
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B168" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C168" t="s">
         <v>40</v>
@@ -4469,10 +4466,10 @@
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B169" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C169" t="s">
         <v>40</v>
@@ -4480,10 +4477,10 @@
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B170" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C170" t="s">
         <v>40</v>
@@ -4491,10 +4488,10 @@
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
+        <v>408</v>
+      </c>
+      <c r="B171" t="s">
         <v>409</v>
-      </c>
-      <c r="B171" t="s">
-        <v>410</v>
       </c>
       <c r="C171" t="s">
         <v>40</v>
@@ -4502,32 +4499,32 @@
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B172" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C172" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B173" t="s">
+        <v>411</v>
+      </c>
+      <c r="C173" t="s">
         <v>412</v>
-      </c>
-      <c r="C173" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B174" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C174" t="s">
         <v>233</v>
@@ -4535,178 +4532,178 @@
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
+        <v>414</v>
+      </c>
+      <c r="B175" t="s">
         <v>415</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C175" t="s">
         <v>416</v>
-      </c>
-      <c r="C175" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B176" t="s">
+        <v>417</v>
+      </c>
+      <c r="C176" t="s">
         <v>418</v>
-      </c>
-      <c r="C176" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B177" t="s">
+        <v>419</v>
+      </c>
+      <c r="C177" t="s">
         <v>420</v>
-      </c>
-      <c r="C177" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B178" t="s">
+        <v>421</v>
+      </c>
+      <c r="C178" t="s">
         <v>422</v>
-      </c>
-      <c r="C178" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
+        <v>423</v>
+      </c>
+      <c r="B179" t="s">
         <v>424</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C179" t="s">
         <v>425</v>
-      </c>
-      <c r="C179" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B180" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C180" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B181" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C181" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B182" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C182" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
+        <v>429</v>
+      </c>
+      <c r="B183" t="s">
         <v>430</v>
       </c>
-      <c r="B183" t="s">
-        <v>431</v>
-      </c>
       <c r="C183" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B184" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C184" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B185" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C185" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B186" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C186" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
+        <v>434</v>
+      </c>
+      <c r="B187" t="s">
         <v>435</v>
       </c>
-      <c r="B187" t="s">
-        <v>436</v>
-      </c>
       <c r="C187" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B188" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C188" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B189" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C189" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B190" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C190" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -4923,7 +4920,7 @@
         <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4967,7 +4964,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4978,7 +4975,7 @@
         <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5022,7 +5019,7 @@
         <v>69</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5088,7 +5085,7 @@
         <v>81</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -5231,7 +5228,7 @@
         <v>113</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -5319,7 +5316,7 @@
         <v>134</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -5539,7 +5536,7 @@
         <v>182</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -5561,7 +5558,7 @@
         <v>188</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -5660,7 +5657,7 @@
         <v>212</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -5748,7 +5745,7 @@
         <v>230</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -5770,7 +5767,7 @@
         <v>235</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -5825,7 +5822,7 @@
         <v>246</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -5932,7 +5929,7 @@
         <v>268</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -6003,65 +6000,65 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="C117" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="C118" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C120" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C121" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>54</v>
@@ -6069,98 +6066,98 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="C123" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="C124" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="C125" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="C126" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="C127" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C130" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>324</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>98</v>
@@ -6168,10 +6165,10 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>28</v>
@@ -6179,10 +6176,10 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>98</v>
@@ -6190,164 +6187,164 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="C134" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C136" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C137" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C138" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C139" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C140" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C141" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C142" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="C143" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="C144" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="C145" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="C146" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="C147" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>224</v>
@@ -6355,10 +6352,10 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>366</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>125</v>
@@ -6366,10 +6363,10 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>369</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>122</v>
@@ -6377,10 +6374,10 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>28</v>
@@ -6388,10 +6385,10 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>119</v>
@@ -6399,21 +6396,21 @@
     </row>
     <row r="153" spans="1:3">
       <c r="A153" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="C153" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>101</v>
@@ -6421,10 +6418,10 @@
     </row>
     <row r="155" spans="1:3">
       <c r="A155" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>54</v>
@@ -6432,21 +6429,21 @@
     </row>
     <row r="156" spans="1:3">
       <c r="A156" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="C156" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>122</v>
@@ -6454,21 +6451,21 @@
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="C158" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>389</v>
       </c>
       <c r="C159" s="1">
         <v>450</v>
@@ -6476,10 +6473,10 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>392</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>5</v>
@@ -6487,32 +6484,32 @@
     </row>
     <row r="161" spans="1:3">
       <c r="A161" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="C161" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="C162" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>40</v>
@@ -6520,10 +6517,10 @@
     </row>
     <row r="164" spans="1:3">
       <c r="A164" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>40</v>
@@ -6531,10 +6528,10 @@
     </row>
     <row r="165" spans="1:3">
       <c r="A165" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>40</v>
@@ -6542,10 +6539,10 @@
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>40</v>
@@ -6553,10 +6550,10 @@
     </row>
     <row r="167" spans="1:3">
       <c r="A167" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>40</v>
@@ -6564,10 +6561,10 @@
     </row>
     <row r="168" spans="1:3">
       <c r="A168" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>40</v>
@@ -6575,10 +6572,10 @@
     </row>
     <row r="169" spans="1:3">
       <c r="A169" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>40</v>
@@ -6586,10 +6583,10 @@
     </row>
     <row r="170" spans="1:3">
       <c r="A170" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>40</v>
@@ -6597,10 +6594,10 @@
     </row>
     <row r="171" spans="1:3">
       <c r="A171" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>410</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>40</v>
@@ -6608,10 +6605,10 @@
     </row>
     <row r="172" spans="1:3">
       <c r="A172" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>40</v>
@@ -6619,10 +6616,10 @@
     </row>
     <row r="173" spans="1:3">
       <c r="A173" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>40</v>
@@ -6630,10 +6627,10 @@
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>40</v>
@@ -6641,178 +6638,178 @@
     </row>
     <row r="175" spans="1:3">
       <c r="A175" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>416</v>
-      </c>
       <c r="C175" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="C179" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="C183" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="C187" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
